--- a/12609499.xlsx
+++ b/12609499.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sania\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB52F1C-7D75-4CD1-9B9B-90513272A531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6236BD7B-F593-469B-BC31-897A517ADE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>MCA</t>
+  </si>
+  <si>
+    <t>feleling great</t>
   </si>
 </sst>
 </file>
@@ -1446,26 +1449,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B15" s="14">
+        <v>360</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>300</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>100</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
+        <v>60</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12609499.xlsx
+++ b/12609499.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6236BD7B-F593-469B-BC31-897A517ADE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582F917E-8817-4F5B-8557-5B3D74B3F7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -243,7 +243,10 @@
     <t>MCA</t>
   </si>
   <si>
-    <t>feleling great</t>
+    <t>feeling great</t>
+  </si>
+  <si>
+    <t>i am attending ca viva</t>
   </si>
 </sst>
 </file>
@@ -1495,26 +1498,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B16" s="14">
+        <v>300</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>400</v>
+      </c>
+      <c r="E16" s="14">
+        <v>30</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12609499.xlsx
+++ b/12609499.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582F917E-8817-4F5B-8557-5B3D74B3F7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6922529D-B2A6-4D16-8C0A-E9508DF77F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>i am attending ca viva</t>
+  </si>
+  <si>
+    <t>I am attending today a  makeup class</t>
   </si>
 </sst>
 </file>
@@ -1543,27 +1546,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B17" s="14">
+        <v>350</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>400</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>100</v>
+      </c>
+      <c r="G17" s="14">
+        <v>2</v>
+      </c>
+      <c r="H17" s="14">
+        <v>60</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12609499.xlsx
+++ b/12609499.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6922529D-B2A6-4D16-8C0A-E9508DF77F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF3D797-A7A8-4BD0-8171-55C08D08D766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,15 @@
   </si>
   <si>
     <t>I am attending today a  makeup class</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>this day is not good day for me and everyone of university</t>
+  </si>
+  <si>
+    <t>I am going to a  home because the university gave a holiday</t>
   </si>
 </sst>
 </file>
@@ -1592,49 +1601,93 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B18" s="14">
+        <v>400</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>360</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>120</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+        <v>410</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>46293</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="D19" s="14">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>120</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>120</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>1320</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12609499.xlsx
+++ b/12609499.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF3D797-A7A8-4BD0-8171-55C08D08D766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E4613D-2F38-41D7-84F5-92973E984476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t>I am going to a  home because the university gave a holiday</t>
+  </si>
+  <si>
+    <t>I am happy .</t>
+  </si>
+  <si>
+    <t>I am getting prepartion for mid term exam</t>
   </si>
 </sst>
 </file>
@@ -1690,48 +1696,88 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13">
+        <v>46294</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="D20" s="14">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>300</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
+        <v>780</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46295</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="D21" s="14">
+        <v>350</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>850</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12609499.xlsx
+++ b/12609499.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E4613D-2F38-41D7-84F5-92973E984476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9496C2-C0C1-4119-8310-0A95D83A4852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>Sleep (min)</t>
-  </si>
-  <si>
-    <t>Fitness (min)</t>
   </si>
   <si>
     <t>Study (min)</t>
@@ -265,6 +262,12 @@
   </si>
   <si>
     <t>I am getting prepartion for mid term exam</t>
+  </si>
+  <si>
+    <t>fitness</t>
+  </si>
+  <si>
+    <t>I am getting revision to the mid term exam</t>
   </si>
 </sst>
 </file>
@@ -414,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -457,6 +460,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -896,7 +902,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -944,74 +950,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12609499</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="B3" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="21"/>
+      <c r="F3" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1020,41 +1026,41 @@
       <c r="B5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1089,16 +1095,16 @@
         <v>120</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="M6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N6" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1135,16 +1141,16 @@
         <v>280</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>56</v>
-      </c>
       <c r="N7" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1181,16 +1187,16 @@
         <v>500</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="M8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="N8" s="17" t="s">
         <v>61</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1227,16 +1233,16 @@
         <v>250</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="M9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N9" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1273,16 +1279,16 @@
         <v>490</v>
       </c>
       <c r="K10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="M10" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N10" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1319,16 +1325,16 @@
         <v>400</v>
       </c>
       <c r="K11" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N11" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1365,16 +1371,16 @@
         <v>400</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="M12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N12" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1411,16 +1417,16 @@
         <v>360</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1457,16 +1463,16 @@
         <v>310</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="17" t="s">
-        <v>51</v>
-      </c>
       <c r="N14" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1503,16 +1509,16 @@
         <v>530</v>
       </c>
       <c r="K15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="M15" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M15" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N15" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1549,16 +1555,16 @@
         <v>290</v>
       </c>
       <c r="K16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="M16" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N16" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1595,16 +1601,16 @@
         <v>470</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1641,24 +1647,28 @@
         <v>410</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L18" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>46293</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="14">
+        <v>300</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
       <c r="D19" s="14">
         <v>0</v>
       </c>
@@ -1676,31 +1686,35 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>1320</v>
+        <v>1020</v>
       </c>
       <c r="K19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="M19" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M19" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N19" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>46294</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
+      <c r="B20" s="14">
+        <v>400</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
       <c r="D20" s="14">
         <v>300</v>
       </c>
@@ -1718,31 +1732,35 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>1060</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>380</v>
       </c>
       <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="M20" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M20" s="16" t="s">
-        <v>61</v>
-      </c>
       <c r="N20" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>46295</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="14">
+        <v>350</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
       <c r="D21" s="14">
         <v>350</v>
       </c>
@@ -1760,46 +1778,70 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>590</v>
+        <v>940</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="K21" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="M21" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M21" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N21" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>400</v>
+      </c>
+      <c r="E22" s="14">
+        <v>60</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>60</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12609499.xlsx
+++ b/12609499.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9496C2-C0C1-4119-8310-0A95D83A4852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C61A71-5CCC-4E94-AC55-C462097495F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -246,28 +246,7 @@
     <t>i am attending ca viva</t>
   </si>
   <si>
-    <t>I am attending today a  makeup class</t>
-  </si>
-  <si>
-    <t>Unsatisfied</t>
-  </si>
-  <si>
-    <t>this day is not good day for me and everyone of university</t>
-  </si>
-  <si>
-    <t>I am going to a  home because the university gave a holiday</t>
-  </si>
-  <si>
-    <t>I am happy .</t>
-  </si>
-  <si>
-    <t>I am getting prepartion for mid term exam</t>
-  </si>
-  <si>
     <t>fitness</t>
-  </si>
-  <si>
-    <t>I am getting revision to the mid term exam</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1006,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>37</v>
@@ -1567,281 +1546,116 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
-        <v>46291</v>
-      </c>
-      <c r="B17" s="14">
-        <v>350</v>
-      </c>
-      <c r="C17" s="14">
-        <v>0</v>
-      </c>
-      <c r="D17" s="14">
-        <v>400</v>
-      </c>
-      <c r="E17" s="14">
-        <v>60</v>
-      </c>
-      <c r="F17" s="14">
-        <v>100</v>
-      </c>
-      <c r="G17" s="14">
-        <v>2</v>
-      </c>
-      <c r="H17" s="14">
-        <v>60</v>
-      </c>
-      <c r="I17" s="15">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="17"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="17"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="13"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="17"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>970</v>
-      </c>
-      <c r="J17" s="15">
+        <v/>
+      </c>
+      <c r="J20" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>470</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
-        <v>46292</v>
-      </c>
-      <c r="B18" s="14">
-        <v>400</v>
-      </c>
-      <c r="C18" s="14">
-        <v>30</v>
-      </c>
-      <c r="D18" s="14">
-        <v>360</v>
-      </c>
-      <c r="E18" s="14">
-        <v>120</v>
-      </c>
-      <c r="F18" s="14">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14">
-        <v>0</v>
-      </c>
-      <c r="H18" s="14">
-        <v>120</v>
-      </c>
-      <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>1030</v>
-      </c>
-      <c r="J18" s="15">
+        <v/>
+      </c>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="17"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>410</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B19" s="14">
-        <v>300</v>
-      </c>
-      <c r="C19" s="14">
-        <v>0</v>
-      </c>
-      <c r="D19" s="14">
-        <v>0</v>
-      </c>
-      <c r="E19" s="14">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14">
-        <v>0</v>
-      </c>
-      <c r="H19" s="14">
-        <v>120</v>
-      </c>
-      <c r="I19" s="15">
-        <f t="shared" si="0"/>
-        <v>420</v>
-      </c>
-      <c r="J19" s="15">
+        <v/>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="17"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>1020</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
-        <v>46294</v>
-      </c>
-      <c r="B20" s="14">
-        <v>400</v>
-      </c>
-      <c r="C20" s="14">
-        <v>0</v>
-      </c>
-      <c r="D20" s="14">
-        <v>300</v>
-      </c>
-      <c r="E20" s="14">
-        <v>60</v>
-      </c>
-      <c r="F20" s="14">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>300</v>
-      </c>
-      <c r="I20" s="15">
-        <f t="shared" si="0"/>
-        <v>1060</v>
-      </c>
-      <c r="J20" s="15">
-        <f t="shared" si="1"/>
-        <v>380</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="13">
-        <v>46295</v>
-      </c>
-      <c r="B21" s="14">
-        <v>350</v>
-      </c>
-      <c r="C21" s="14">
-        <v>0</v>
-      </c>
-      <c r="D21" s="14">
-        <v>350</v>
-      </c>
-      <c r="E21" s="14">
-        <v>120</v>
-      </c>
-      <c r="F21" s="14">
-        <v>0</v>
-      </c>
-      <c r="G21" s="14">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14">
-        <v>120</v>
-      </c>
-      <c r="I21" s="15">
-        <f t="shared" si="0"/>
-        <v>940</v>
-      </c>
-      <c r="J21" s="15">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
-        <v>46296</v>
-      </c>
-      <c r="B22" s="14">
-        <v>300</v>
-      </c>
-      <c r="C22" s="14">
-        <v>0</v>
-      </c>
-      <c r="D22" s="14">
-        <v>400</v>
-      </c>
-      <c r="E22" s="14">
-        <v>60</v>
-      </c>
-      <c r="F22" s="14">
-        <v>0</v>
-      </c>
-      <c r="G22" s="14">
-        <v>0</v>
-      </c>
-      <c r="H22" s="14">
-        <v>60</v>
-      </c>
-      <c r="I22" s="15">
-        <f t="shared" si="0"/>
-        <v>820</v>
-      </c>
-      <c r="J22" s="15">
-        <f t="shared" si="1"/>
-        <v>620</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>76</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
@@ -10176,7 +9990,6 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K401" s="16"/>
       <c r="L401" s="16"/>
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
@@ -10196,10 +10009,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401 M13" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
@@ -10208,6 +10017,10 @@
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/12609499.xlsx
+++ b/12609499.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C61A71-5CCC-4E94-AC55-C462097495F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2390BDCE-2DCD-4EAA-B5C4-2F06119C8E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -246,7 +246,10 @@
     <t>i am attending ca viva</t>
   </si>
   <si>
-    <t>fitness</t>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>fitness (min)</t>
   </si>
 </sst>
 </file>
@@ -396,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -442,6 +445,9 @@
     </xf>
     <xf numFmtId="1" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -929,74 +935,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="23">
         <v>12609499</v>
       </c>
-      <c r="G2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1006,7 +1012,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>37</v>
@@ -1050,7 +1056,7 @@
         <v>360</v>
       </c>
       <c r="C6" s="9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="9">
         <v>240</v>
@@ -1068,10 +1074,10 @@
         <v>60</v>
       </c>
       <c r="I6" s="10">
-        <v>90</v>
+        <v>1130</v>
       </c>
       <c r="J6" s="10">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>48</v>
@@ -1158,7 +1164,7 @@
         <v>60</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
         <v>940</v>
       </c>
       <c r="J8" s="15">
@@ -1402,7 +1408,7 @@
         <v>54</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="N13" s="18" t="s">
         <v>65</v>
@@ -1655,7 +1661,7 @@
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+      <c r="N22" s="20"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
@@ -10023,6 +10029,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>